--- a/reports/tables/Full_vs_11feature_metrics.xlsx
+++ b/reports/tables/Full_vs_11feature_metrics.xlsx
@@ -517,49 +517,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6629</v>
+        <v>0.6716</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0993</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2223</v>
+        <v>0.2211</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0654</v>
+        <v>0.068</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0588</v>
+        <v>0.0805</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8048999999999999</v>
+        <v>0.5854</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5396</v>
+        <v>0.6673</v>
       </c>
       <c r="I2" t="n">
-        <v>0.974</v>
+        <v>0.9562</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1142</v>
+        <v>0.1148</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5578</v>
+        <v>0.6616</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0.192</v>
       </c>
       <c r="M2" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="N2" t="n">
-        <v>256</v>
+        <v>185</v>
       </c>
       <c r="O2" t="n">
-        <v>300</v>
+        <v>371</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -569,49 +569,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6831</v>
+        <v>0.6803</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1098</v>
+        <v>0.1175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2329</v>
+        <v>0.2325</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0669</v>
+        <v>0.0679</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7805</v>
+        <v>0.7317</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5522</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9708</v>
+        <v>0.9654</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1107</v>
+        <v>0.1075</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5544</v>
+        <v>0.5645</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1939</v>
+        <v>0.1875</v>
       </c>
       <c r="M3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N3" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="O3" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
